--- a/artfynd/A 3410-2023 artfynd.xlsx
+++ b/artfynd/A 3410-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3410-2023 artfynd.xlsx
+++ b/artfynd/A 3410-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72434575</v>
+        <v>72434600</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>431206</v>
+        <v>431187</v>
       </c>
       <c r="R2" t="n">
-        <v>6477250</v>
+        <v>6477245</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -778,23 +773,14 @@
           <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Billingens flora</t>
-        </is>
-      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>72434600</v>
+        <v>121404563</v>
       </c>
       <c r="B3" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,37 +788,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>102125</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rydsgrottor väster om, Vg</t>
+          <t>Ryds grottor, Ryds grottor, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>431187.1885003974</v>
+        <v>431189</v>
       </c>
       <c r="R3" t="n">
-        <v>6477244.608453296</v>
+        <v>6477182</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,27 +851,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-05-12</t>
+          <t>2024-11-30</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-05-12</t>
+          <t>2024-11-30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Skövde kommuns skogsbruksplan - Östra Billingen objekt 11</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,15 +881,343 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Petter Bohman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>108306411</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>sträckande S</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ryds Grottor, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>431256</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6477261</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-09-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Hallqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Hallqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>72434575</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rydsgrottor väster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>431206</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6477250</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-05-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-05-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Skövde kommuns skogsbruksplan - Östra Billingen objekt 11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>72434578</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rydsgrottor väster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>431194</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6477292</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-05-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-05-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Skövde kommuns skogsbruksplan - Östra Billingen objekt 11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3410-2023 artfynd.xlsx
+++ b/artfynd/A 3410-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72434600</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121404563</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108306411</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72434575</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,8 +1243,20 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72434578</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>